--- a/Estimates comparison.xlsx
+++ b/Estimates comparison.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tarun\Documents\GitHub\appliances_interventions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92893757-AAC7-40BD-AF80-90EAF526E5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EC16F8-CAF9-4A1B-BD95-DC7593C46222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0C6B4E0-0F2C-44EE-A3B4-7216DC8C5C64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D0C6B4E0-0F2C-44EE-A3B4-7216DC8C5C64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="26">
   <si>
     <t>interventionInformation</t>
   </si>
@@ -105,6 +106,15 @@
   </si>
   <si>
     <t>&lt;.0001</t>
+  </si>
+  <si>
+    <t>intrcpt</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>2 rows</t>
   </si>
 </sst>
 </file>
@@ -114,7 +124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +142,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
       <name val="Lucida Sans"/>
       <family val="2"/>
     </font>
@@ -163,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -180,6 +196,9 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1785,4 +1804,133 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBE2AE2-2443-4B09-A24C-2A000F41C31C}">
+  <dimension ref="B3:J8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="9" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1.0646</v>
+      </c>
+      <c r="F3" s="5">
+        <v>20.45</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="H3" s="5">
+        <v>-3.2599999999999997E-2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.1007</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.5089999999999999</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.60060000000000002</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2.5125999999999999</v>
+      </c>
+      <c r="F4" s="5">
+        <v>6.76</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2.9392999999999998</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9.9400000000000002E-2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2.01E-2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4.9367999999999999</v>
+      </c>
+      <c r="F6" s="5">
+        <v>37.94</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.14019999999999999</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3.1475</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.3905000000000001</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2.2635999999999998</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.1875</v>
+      </c>
+      <c r="H7" s="5">
+        <v>-4.8452999999999999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>11.1402</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>